--- a/projects/skill_modify_excel_with_r/statistischer_bericht_klinische_studie.xlsx
+++ b/projects/skill_modify_excel_with_r/statistischer_bericht_klinische_studie.xlsx
@@ -38,12 +38,12 @@
     <numFmt numFmtId="166" formatCode="0,00"/>
     <numFmt numFmtId="167" formatCode="0,00"/>
     <numFmt numFmtId="168" formatCode="0,00"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="0,00"/>
+    <numFmt numFmtId="170" formatCode="0,00"/>
+    <numFmt numFmtId="171" formatCode="0,00"/>
+    <numFmt numFmtId="172" formatCode="0,00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,25 +54,26 @@
     <font>
       <b val="1"/>
       <color rgb="FF004B76"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="14"/>
     </font>
     <font>
+      <b val="0"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="12"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="FF004B76"/>
-      <name val="Aptos Narrow"/>
-      <sz val="14"/>
+      <b val="0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <color theme="10"/>
@@ -82,31 +83,41 @@
     </font>
     <font>
       <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF004B76"/>
+      <name val="Arial"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <sz val="16"/>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF004B76"/>
-      <name val="Aptos Narrow"/>
-      <sz val="12"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -140,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
@@ -149,22 +160,31 @@
     <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="165" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="166" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="166" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="167" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="168" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="169" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="171" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="172" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -515,16 +535,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EVAS-Nummer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>61241</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>EVAS-Nummer: 61241</t>
         </is>
       </c>
     </row>
@@ -539,103 +552,104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-02: Klinische Studie - Demografische und Wirksamkeitsdaten</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Altersgruppe</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Anzahl_Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Anzahl_Placebo</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Event_Rate_Gesamt_Medikament 1</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Event_Rate_Gesamt_Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>&lt;40 Jahre</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="27">
         <v>20</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="28">
         <v>31</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>15 (75%)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>20 (64.5%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>≥40 Jahre</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="27">
         <v>49</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="28">
         <v>63</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>26 (53.1%)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>39 (61.9%)</t>
         </is>
@@ -657,87 +671,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-02-b: Tabelle mit 2 Zeilen und 5 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-02. Sie erstreckt sich über 5 Spalten und 2 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Altersgruppe</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Anzahl_Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Anzahl_Placebo</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Event_Rate_Gesamt_Medikament 1</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Event_Rate_Gesamt_Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>&lt;40 Jahre</t>
         </is>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="31">
         <v>20</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="32">
         <v>31</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>15 (75%)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>20 (64.5%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>≥40 Jahre</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="31">
         <v>49</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="32">
         <v>63</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>26 (53.1%)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>39 (61.9%)</t>
         </is>
@@ -755,106 +784,115 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-02</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Altersgruppe</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Anzahl_Medikament 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Anzahl_Placebo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Event_Rate_Gesamt_Medikament 1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Event_Rate_Gesamt_Placebo</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>&lt;40 Jahre</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="B5" s="8">
         <v>20</v>
       </c>
-      <c r="D2">
+      <c r="C5" s="8">
         <v>31</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>15 (75%)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>20 (64.5%)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>≥40 Jahre</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="B6" s="8">
         <v>49</v>
       </c>
-      <c r="D3">
+      <c r="C6" s="8">
         <v>63</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>26 (53.1%)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>39 (61.9%)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -865,78 +903,76 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-03: Klinische Studie - Demografische und Wirksamkeitsdaten</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Ereignisrate (n/N, %)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>41/69 (59.4%)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>59/94 (62.8%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Ereignisrate (%)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>59.4%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>62.8%</t>
         </is>
@@ -958,65 +994,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-03-b: Tabelle mit 2 Zeilen und 3 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-03. Sie erstreckt sich über 3 Spalten und 2 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Ereignisrate (n/N, %)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>41/69 (59.4%)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>59/94 (62.8%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Ereignisrate (%)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>59.4%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>62.8%</t>
         </is>
@@ -1034,81 +1079,87 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="4" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-03</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Ereignisrate (n/N, %)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>41/69 (59.4%)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>59/94 (62.8%)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Ereignisrate (%)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>59.4%</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>62.8%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1119,79 +1170,76 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-04: Klinische Studie - Demografische und Wirksamkeitsdaten</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Geschlecht</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Männlich</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>37 (53.6%)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>62 (66%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Weiblich</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>32 (46.4%)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>32 (34%)</t>
         </is>
@@ -1213,65 +1261,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-04-b: Tabelle mit 2 Zeilen und 3 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-04. Sie erstreckt sich über 3 Spalten und 2 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Geschlecht</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Männlich</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>37 (53.6%)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>62 (66%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Weiblich</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>32 (46.4%)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>32 (34%)</t>
         </is>
@@ -1289,82 +1346,87 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-04</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Geschlecht</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Männlich</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>37 (53.6%)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>62 (66%)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Weiblich</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>32 (46.4%)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>32 (34%)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1375,96 +1437,93 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-05: Klinische Studie - Demografische und Wirksamkeitsdaten</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Ethnische_Zugehörigkeit</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Andere</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>5 (7.2%)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>13 (13.8%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Asiatisch</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>17 (24.6%)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>15 (16%)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Europäisch</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>47 (68.1%)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>66 (70.2%)</t>
         </is>
@@ -1482,33 +1541,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Informationen zur Barrierefreiheit</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>zur Inhaltsübersicht</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Diese Publikation enthält eine oder mehrere barrierefreie Tabellen, die durch die Tabellenbezeichnung "-b" erkennbar und am Anfang des Tabellenteils zu finden sind.</t>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Dieses Dokument wurde nach den Richtlinien für Barrierefreiheit erstellt.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A1" r:id="rId1"/>
   </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1522,82 +1581,91 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-05-b: Tabelle mit 3 Zeilen und 3 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-05. Sie erstreckt sich über 3 Spalten und 3 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Ethnische_Zugehörigkeit</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Andere</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>5 (7.2%)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>13 (13.8%)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Asiatisch</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>17 (24.6%)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>15 (16%)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Europäisch</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>47 (68.1%)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>66 (70.2%)</t>
         </is>
@@ -1615,104 +1683,104 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-05</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Ethnische_Zugehörigkeit</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Andere</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>5 (7.2%)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>13 (13.8%)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Asiatisch</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>17 (24.6%)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>15 (16%)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Europäisch</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>47 (68.1%)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>66 (70.2%)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1721,146 +1789,130 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-  </cols>
   <sheetData>
-    <row customHeight="1" ht="25" r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Inhaltsübersicht</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Informationen zur Barrierefreiheit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>GENESIS-Online</t>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Übersicht GENESIS-Online</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Impressum</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Informationen zur Statistik</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Barrierefreie Tabellen</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Tabellen</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>61241-01 - Layout-Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>61241-01 -b - Barrierefreie Tabelle</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>61241-02 - Layout-Tabelle</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>61241-01</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>61241-02 -b - Barrierefreie Tabelle</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>61241-02</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>61241-03 - Layout-Tabelle</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>61241-03</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>61241-03 -b - Barrierefreie Tabelle</t>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>61241-04</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>61241-04 - Layout-Tabelle</t>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>61241-05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>61241-04 -b - Barrierefreie Tabelle</t>
-        </is>
-      </c>
+      <c r="A15" s="11"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>61241-05 - Layout-Tabelle</t>
-        </is>
-      </c>
+      <c r="A16" s="11"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>61241-05 -b - Barrierefreie Tabelle</t>
-        </is>
-      </c>
+      <c r="A17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
     <hyperlink ref="A3" r:id="rId2"/>
     <hyperlink ref="A4" r:id="rId3"/>
     <hyperlink ref="A5" r:id="rId4"/>
-    <hyperlink ref="A8" r:id="rId5"/>
-    <hyperlink ref="A9" r:id="rId6"/>
-    <hyperlink ref="A10" r:id="rId7"/>
-    <hyperlink ref="A11" r:id="rId8"/>
-    <hyperlink ref="A12" r:id="rId9"/>
-    <hyperlink ref="A13" r:id="rId10"/>
-    <hyperlink ref="A14" r:id="rId11"/>
-    <hyperlink ref="A15" r:id="rId12"/>
-    <hyperlink ref="A16" r:id="rId13"/>
-    <hyperlink ref="A17" r:id="rId14"/>
+    <hyperlink ref="A10" r:id="rId5"/>
+    <hyperlink ref="A11" r:id="rId6"/>
+    <hyperlink ref="A12" r:id="rId7"/>
+    <hyperlink ref="A13" r:id="rId8"/>
+    <hyperlink ref="A14" r:id="rId9"/>
   </hyperlinks>
-  <printOptions gridLines="1" gridLinesSet="1"/>
+  <printOptions gridLines="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1868,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -1878,8 +1930,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>GENESIS-Online</t>
         </is>
@@ -1897,7 +1949,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -1907,8 +1959,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Impressum</t>
         </is>
@@ -1926,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -1936,8 +1988,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Informationen zur Statistik</t>
         </is>
@@ -1957,177 +2009,174 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-01: Klinische Studie - Demografische und Wirksamkeitsdaten</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Anzahl Teilnehmer (n)</t>
         </is>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="18">
         <v>69</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="19">
         <v>94</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Alter Mittelwert (Jahre)</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="18">
         <v>47.5</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>45.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Alter Standardabweichung (Jahre)</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="18">
         <v>11.2</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>10.8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Alter Median (Jahre)</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="18">
         <v>48</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="19">
         <v>46</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Alter Minimum (Jahre)</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="18">
         <v>27</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>27</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Alter Maximum (Jahre)</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="18">
         <v>65</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="19">
         <v>65</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>BMI Mittelwert (kg/m²)</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="18">
         <v>26.1</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="19">
         <v>25.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>BMI Standardabweichung (kg/m²)</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="18">
         <v>3.8</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="19">
         <v>4.2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Anteil männlich (%)</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="18">
         <v>53.6</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="19">
         <v>66</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Anteil weiblich (%)</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="18">
         <v>46.4</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="19">
         <v>34</v>
       </c>
     </row>
@@ -2147,163 +2196,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-01-b: Tabelle mit 10 Zeilen und 3 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-01. Sie erstreckt sich über 3 Spalten und 10 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Anzahl Teilnehmer (n)</t>
         </is>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="23">
         <v>69</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="24">
         <v>94</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Alter Mittelwert (Jahre)</t>
         </is>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="23">
         <v>47.5</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="24">
         <v>45.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Alter Standardabweichung (Jahre)</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="23">
         <v>11.2</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="24">
         <v>10.8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Alter Median (Jahre)</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="23">
         <v>48</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="24">
         <v>46</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Alter Minimum (Jahre)</t>
         </is>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="23">
         <v>27</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="24">
         <v>27</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Alter Maximum (Jahre)</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="23">
         <v>65</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="24">
         <v>65</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>BMI Mittelwert (kg/m²)</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="23">
         <v>26.1</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="24">
         <v>25.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>BMI Standardabweichung (kg/m²)</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="23">
         <v>3.8</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="24">
         <v>4.2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Anteil männlich (%)</t>
         </is>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="23">
         <v>53.6</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="24">
         <v>66</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Anteil weiblich (%)</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="23">
         <v>46.4</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="24">
         <v>34</v>
       </c>
     </row>
@@ -2319,218 +2377,183 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-01</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Medikament 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Anzahl Teilnehmer (n)</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="B5" s="8">
         <v>69</v>
       </c>
-      <c r="D2">
+      <c r="C5" s="8">
         <v>94</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Alter Mittelwert (Jahre)</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="B6" s="8">
         <v>47.5</v>
       </c>
-      <c r="D3">
+      <c r="C6" s="8">
         <v>45.8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Alter Standardabweichung (Jahre)</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="B7" s="8">
         <v>11.2</v>
       </c>
-      <c r="D4">
+      <c r="C7" s="8">
         <v>10.8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Alter Median (Jahre)</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="B8" s="8">
         <v>48</v>
       </c>
-      <c r="D5">
+      <c r="C8" s="8">
         <v>46</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Alter Minimum (Jahre)</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="B9" s="8">
         <v>27</v>
       </c>
-      <c r="D6">
+      <c r="C9" s="8">
         <v>27</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Alter Maximum (Jahre)</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="B10" s="8">
         <v>65</v>
       </c>
-      <c r="D7">
+      <c r="C10" s="8">
         <v>65</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>BMI Mittelwert (kg/m²)</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="B11" s="8">
         <v>26.1</v>
       </c>
-      <c r="D8">
+      <c r="C11" s="8">
         <v>25.7</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>BMI Standardabweichung (kg/m²)</t>
         </is>
       </c>
-      <c r="C9">
+      <c r="B12" s="8">
         <v>3.8</v>
       </c>
-      <c r="D9">
+      <c r="C12" s="8">
         <v>4.2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Anteil männlich (%)</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="B13" s="8">
         <v>53.6</v>
       </c>
-      <c r="D10">
+      <c r="C13" s="8">
         <v>66</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Anteil weiblich (%)</t>
         </is>
       </c>
-      <c r="C11">
+      <c r="B14" s="8">
         <v>46.4</v>
       </c>
-      <c r="D11">
+      <c r="C14" s="8">
         <v>34</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
